--- a/artfynd/A 44528-2026 artfynd.xlsx
+++ b/artfynd/A 44528-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137454058</v>
       </c>
       <c r="B2" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>137454042</v>
       </c>
       <c r="B5" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
